--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260616.xlsx
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>10,849,000</t>
+          <t>46,711,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>46,711,000</t>
+          <t>10,849,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>13,403,000</t>
+          <t>1,976,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,976,000</t>
+          <t>13,403,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>30,294,200</t>
+          <t>34,455,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>34,455,000</t>
+          <t>30,294,200</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,350,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>7,350,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>591,000</t>
+          <t>244,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>244,000</t>
+          <t>1,007,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>1,007,000</t>
+          <t>591,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,819,000</t>
+          <t>905,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>905,000</t>
+          <t>1,819,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>224,000</t>
+          <t>335,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>335,000</t>
+          <t>224,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
